--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>662.46</v>
+        <v>624.89</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>562.39</v>
+        <v>550.26</v>
       </c>
       <c r="F2">
-        <v>523.2</v>
+        <v>488.75</v>
       </c>
       <c r="G2">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="H2">
-        <v>882</v>
+        <v>839</v>
       </c>
       <c r="I2">
-        <v>23325</v>
+        <v>14781</v>
       </c>
       <c r="J2">
-        <v>3.682364402488119</v>
+        <v>4.52601548338887</v>
       </c>
       <c r="K2">
-        <v>655.2423238428039</v>
+        <v>616.0184461502446</v>
       </c>
       <c r="L2">
-        <v>669.6776761571962</v>
+        <v>633.7615538497554</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>469.08</v>
+        <v>443.5</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,28 +469,28 @@
         <v>6206.75</v>
       </c>
       <c r="E3">
-        <v>511.23</v>
+        <v>498.31</v>
       </c>
       <c r="F3">
-        <v>336</v>
+        <v>309.64</v>
       </c>
       <c r="G3">
-        <v>103.2</v>
+        <v>84</v>
       </c>
       <c r="H3">
-        <v>664.78</v>
+        <v>630</v>
       </c>
       <c r="I3">
-        <v>23325</v>
+        <v>14781</v>
       </c>
       <c r="J3">
-        <v>3.347383761240422</v>
+        <v>4.09871474489788</v>
       </c>
       <c r="K3">
-        <v>462.5189079076026</v>
+        <v>435.4660087978926</v>
       </c>
       <c r="L3">
-        <v>475.6410920923974</v>
+        <v>451.5339912021074</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>669.9299999999999</v>
+        <v>633.6799999999999</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>561.11</v>
+        <v>549.0700000000001</v>
       </c>
       <c r="F2">
-        <v>530.75</v>
+        <v>501.14</v>
       </c>
       <c r="G2">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="H2">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="I2">
-        <v>23065</v>
+        <v>14576</v>
       </c>
       <c r="J2">
-        <v>3.694632780834341</v>
+        <v>4.547875169560331</v>
       </c>
       <c r="K2">
-        <v>662.6882727786384</v>
+        <v>624.7655881750838</v>
       </c>
       <c r="L2">
-        <v>677.1717272213615</v>
+        <v>642.5944118249161</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>474.37</v>
+        <v>449.74</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,28 +617,28 @@
         <v>6206.75</v>
       </c>
       <c r="E3">
-        <v>511.66</v>
+        <v>499</v>
       </c>
       <c r="F3">
-        <v>336</v>
+        <v>320.75</v>
       </c>
       <c r="G3">
-        <v>118.78</v>
+        <v>84</v>
       </c>
       <c r="H3">
-        <v>672</v>
+        <v>630.4299999999999</v>
       </c>
       <c r="I3">
-        <v>23065</v>
+        <v>14576</v>
       </c>
       <c r="J3">
-        <v>3.369028904567195</v>
+        <v>4.13315189249204</v>
       </c>
       <c r="K3">
-        <v>467.766478141395</v>
+        <v>441.638498368818</v>
       </c>
       <c r="L3">
-        <v>480.973521858605</v>
+        <v>457.841501631182</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>624.89</v>
+        <v>477.52</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>8453.309999999999</v>
       </c>
       <c r="E2">
-        <v>550.26</v>
+        <v>545.15</v>
       </c>
       <c r="F2">
-        <v>488.75</v>
+        <v>336</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>61.2</v>
       </c>
       <c r="H2">
-        <v>839</v>
+        <v>684.9299999999999</v>
       </c>
       <c r="I2">
-        <v>14781</v>
+        <v>17856</v>
       </c>
       <c r="J2">
-        <v>4.52601548338887</v>
+        <v>4.08</v>
       </c>
       <c r="K2">
-        <v>616.0184461502446</v>
+        <v>469.52</v>
       </c>
       <c r="L2">
-        <v>633.7615538497554</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>443.5</v>
+        <v>272.53</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6206.75</v>
+        <v>6208.5</v>
       </c>
       <c r="E3">
-        <v>498.31</v>
+        <v>450.38</v>
       </c>
       <c r="F3">
-        <v>309.64</v>
+        <v>42.06</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>630</v>
+        <v>407.86</v>
       </c>
       <c r="I3">
-        <v>14781</v>
+        <v>17856</v>
       </c>
       <c r="J3">
-        <v>4.09871474489788</v>
+        <v>3.37</v>
       </c>
       <c r="K3">
-        <v>435.4660087978926</v>
+        <v>265.92</v>
       </c>
       <c r="L3">
-        <v>451.5339912021074</v>
+        <v>279.14</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>633.6799999999999</v>
+        <v>831.28</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8453.309999999999</v>
+        <v>9588.709999999999</v>
       </c>
       <c r="E2">
-        <v>549.0700000000001</v>
+        <v>922.85</v>
       </c>
       <c r="F2">
-        <v>501.14</v>
+        <v>546</v>
       </c>
       <c r="G2">
         <v>252</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>1076.75</v>
       </c>
       <c r="I2">
-        <v>14576</v>
+        <v>14254</v>
       </c>
       <c r="J2">
-        <v>4.547875169560331</v>
+        <v>7.73</v>
       </c>
       <c r="K2">
-        <v>624.7655881750838</v>
+        <v>816.13</v>
       </c>
       <c r="L2">
-        <v>642.5944118249161</v>
+        <v>846.4299999999999</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>449.74</v>
+        <v>472.46</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6206.75</v>
+        <v>11494.29</v>
       </c>
       <c r="E3">
-        <v>499</v>
+        <v>772.4299999999999</v>
       </c>
       <c r="F3">
-        <v>320.75</v>
+        <v>183.01</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>630.4299999999999</v>
+        <v>630</v>
       </c>
       <c r="I3">
-        <v>14576</v>
+        <v>14254</v>
       </c>
       <c r="J3">
-        <v>4.13315189249204</v>
+        <v>6.47</v>
       </c>
       <c r="K3">
-        <v>441.638498368818</v>
+        <v>459.78</v>
       </c>
       <c r="L3">
-        <v>457.841501631182</v>
+        <v>485.14</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>477.52</v>
+        <v>523.14</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>8453.309999999999</v>
+        <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>545.15</v>
+        <v>570.14</v>
       </c>
       <c r="F2">
-        <v>336</v>
+        <v>385.38</v>
       </c>
       <c r="G2">
-        <v>61.2</v>
+        <v>84</v>
       </c>
       <c r="H2">
-        <v>684.9299999999999</v>
+        <v>756</v>
       </c>
       <c r="I2">
-        <v>17856</v>
+        <v>22866</v>
       </c>
       <c r="J2">
-        <v>4.08</v>
+        <v>3.77</v>
       </c>
       <c r="K2">
-        <v>469.52</v>
+        <v>515.75</v>
       </c>
       <c r="L2">
-        <v>485.52</v>
+        <v>530.53</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>272.53</v>
+        <v>290.83</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,7 +469,7 @@
         <v>6208.5</v>
       </c>
       <c r="E3">
-        <v>450.38</v>
+        <v>468.09</v>
       </c>
       <c r="F3">
         <v>42.06</v>
@@ -478,19 +478,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>407.86</v>
+        <v>439.8</v>
       </c>
       <c r="I3">
-        <v>17856</v>
+        <v>22866</v>
       </c>
       <c r="J3">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>265.92</v>
+        <v>284.76</v>
       </c>
       <c r="L3">
-        <v>279.14</v>
+        <v>296.9</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>831.28</v>
+        <v>926.92</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9588.709999999999</v>
+        <v>10965.6</v>
       </c>
       <c r="E2">
-        <v>922.85</v>
+        <v>964.4</v>
       </c>
       <c r="F2">
-        <v>546</v>
+        <v>630</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>313.2</v>
       </c>
       <c r="H2">
-        <v>1076.75</v>
+        <v>1187.94</v>
       </c>
       <c r="I2">
-        <v>14254</v>
+        <v>18046</v>
       </c>
       <c r="J2">
-        <v>7.73</v>
+        <v>7.18</v>
       </c>
       <c r="K2">
-        <v>816.13</v>
+        <v>912.85</v>
       </c>
       <c r="L2">
-        <v>846.4299999999999</v>
+        <v>940.99</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>472.46</v>
+        <v>511.98</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>11494.29</v>
+        <v>11402.79</v>
       </c>
       <c r="E3">
-        <v>772.4299999999999</v>
+        <v>809.48</v>
       </c>
       <c r="F3">
-        <v>183.01</v>
+        <v>210.29</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>630</v>
+        <v>672.92</v>
       </c>
       <c r="I3">
-        <v>14254</v>
+        <v>18046</v>
       </c>
       <c r="J3">
-        <v>6.47</v>
+        <v>6.03</v>
       </c>
       <c r="K3">
-        <v>459.78</v>
+        <v>500.17</v>
       </c>
       <c r="L3">
-        <v>485.14</v>
+        <v>523.79</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>523.14</v>
+        <v>623.95</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>570.14</v>
+        <v>565.51</v>
       </c>
       <c r="F2">
-        <v>385.38</v>
+        <v>500.39</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="H2">
-        <v>756</v>
+        <v>840</v>
       </c>
       <c r="I2">
-        <v>22866</v>
+        <v>24669</v>
       </c>
       <c r="J2">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>515.75</v>
+        <v>616.89</v>
       </c>
       <c r="L2">
-        <v>530.53</v>
+        <v>631.01</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>290.83</v>
+        <v>442.21</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6208.5</v>
+        <v>6211</v>
       </c>
       <c r="E3">
-        <v>468.09</v>
+        <v>507.48</v>
       </c>
       <c r="F3">
+        <v>298.35</v>
+      </c>
+      <c r="G3">
         <v>42.06</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
       <c r="H3">
-        <v>439.8</v>
+        <v>630.86</v>
       </c>
       <c r="I3">
-        <v>22866</v>
+        <v>24669</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="K3">
-        <v>284.76</v>
+        <v>435.88</v>
       </c>
       <c r="L3">
-        <v>296.9</v>
+        <v>448.54</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>926.92</v>
+        <v>683.64</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>10965.6</v>
+        <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>964.4</v>
+        <v>589.17</v>
       </c>
       <c r="F2">
-        <v>630</v>
+        <v>538.78</v>
       </c>
       <c r="G2">
-        <v>313.2</v>
+        <v>294</v>
       </c>
       <c r="H2">
-        <v>1187.94</v>
+        <v>893.98</v>
       </c>
       <c r="I2">
-        <v>18046</v>
+        <v>23073</v>
       </c>
       <c r="J2">
-        <v>7.18</v>
+        <v>3.88</v>
       </c>
       <c r="K2">
-        <v>912.85</v>
+        <v>676.04</v>
       </c>
       <c r="L2">
-        <v>940.99</v>
+        <v>691.24</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>511.98</v>
+        <v>485.21</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>11402.79</v>
+        <v>7020.64</v>
       </c>
       <c r="E3">
-        <v>809.48</v>
+        <v>535.63</v>
       </c>
       <c r="F3">
-        <v>210.29</v>
+        <v>336.46</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>119.76</v>
       </c>
       <c r="H3">
         <v>672.92</v>
       </c>
       <c r="I3">
-        <v>18046</v>
+        <v>23073</v>
       </c>
       <c r="J3">
-        <v>6.03</v>
+        <v>3.53</v>
       </c>
       <c r="K3">
-        <v>500.17</v>
+        <v>478.3</v>
       </c>
       <c r="L3">
-        <v>523.79</v>
+        <v>492.12</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>623.95</v>
+        <v>523.14</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>9698.440000000001</v>
       </c>
       <c r="E2">
-        <v>565.51</v>
+        <v>570.14</v>
       </c>
       <c r="F2">
-        <v>500.39</v>
+        <v>385.38</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="H2">
-        <v>840</v>
+        <v>756</v>
       </c>
       <c r="I2">
-        <v>24669</v>
+        <v>22866</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="K2">
-        <v>616.89</v>
+        <v>515.75</v>
       </c>
       <c r="L2">
-        <v>631.01</v>
+        <v>530.53</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>442.21</v>
+        <v>290.83</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6211</v>
+        <v>6208.5</v>
       </c>
       <c r="E3">
-        <v>507.48</v>
+        <v>468.09</v>
       </c>
       <c r="F3">
-        <v>298.35</v>
+        <v>42.06</v>
       </c>
       <c r="G3">
-        <v>42.06</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>630.86</v>
+        <v>439.8</v>
       </c>
       <c r="I3">
-        <v>24669</v>
+        <v>22866</v>
       </c>
       <c r="J3">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>435.88</v>
+        <v>284.76</v>
       </c>
       <c r="L3">
-        <v>448.54</v>
+        <v>296.9</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>683.64</v>
+        <v>926.92</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>10965.6</v>
       </c>
       <c r="E2">
-        <v>589.17</v>
+        <v>964.4</v>
       </c>
       <c r="F2">
-        <v>538.78</v>
+        <v>630</v>
       </c>
       <c r="G2">
-        <v>294</v>
+        <v>313.2</v>
       </c>
       <c r="H2">
-        <v>893.98</v>
+        <v>1187.94</v>
       </c>
       <c r="I2">
-        <v>23073</v>
+        <v>18046</v>
       </c>
       <c r="J2">
-        <v>3.88</v>
+        <v>7.18</v>
       </c>
       <c r="K2">
-        <v>676.04</v>
+        <v>912.85</v>
       </c>
       <c r="L2">
-        <v>691.24</v>
+        <v>940.99</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>485.21</v>
+        <v>511.98</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>7020.64</v>
+        <v>11402.79</v>
       </c>
       <c r="E3">
-        <v>535.63</v>
+        <v>809.48</v>
       </c>
       <c r="F3">
-        <v>336.46</v>
+        <v>210.29</v>
       </c>
       <c r="G3">
-        <v>119.76</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>672.92</v>
       </c>
       <c r="I3">
-        <v>23073</v>
+        <v>18046</v>
       </c>
       <c r="J3">
-        <v>3.53</v>
+        <v>6.03</v>
       </c>
       <c r="K3">
-        <v>478.3</v>
+        <v>500.17</v>
       </c>
       <c r="L3">
-        <v>492.12</v>
+        <v>523.79</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Adjusted.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>523.14</v>
+        <v>863.52</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9698.440000000001</v>
+        <v>13857.42</v>
       </c>
       <c r="E2">
-        <v>570.14</v>
+        <v>797.09</v>
       </c>
       <c r="F2">
-        <v>385.38</v>
+        <v>656.39</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>343.19</v>
       </c>
       <c r="H2">
-        <v>756</v>
+        <v>1133.6</v>
       </c>
       <c r="I2">
-        <v>22866</v>
+        <v>18286</v>
       </c>
       <c r="J2">
-        <v>3.77</v>
+        <v>5.89</v>
       </c>
       <c r="K2">
-        <v>515.75</v>
+        <v>851.97</v>
       </c>
       <c r="L2">
-        <v>530.53</v>
+        <v>875.0700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>290.83</v>
+        <v>483</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6208.5</v>
+        <v>10623.41</v>
       </c>
       <c r="E3">
-        <v>468.09</v>
+        <v>687.97</v>
       </c>
       <c r="F3">
-        <v>42.06</v>
+        <v>243.65</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>439.8</v>
+        <v>717.53</v>
       </c>
       <c r="I3">
-        <v>22866</v>
+        <v>18286</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>5.09</v>
       </c>
       <c r="K3">
-        <v>284.76</v>
+        <v>473.03</v>
       </c>
       <c r="L3">
-        <v>296.9</v>
+        <v>492.97</v>
       </c>
     </row>
   </sheetData>
@@ -570,37 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>926.92</v>
+        <v>1197.08</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>10965.6</v>
+        <v>20962.71</v>
       </c>
       <c r="E2">
-        <v>964.4</v>
+        <v>1311.86</v>
       </c>
       <c r="F2">
-        <v>630</v>
+        <v>797.76</v>
       </c>
       <c r="G2">
-        <v>313.2</v>
+        <v>378</v>
       </c>
       <c r="H2">
-        <v>1187.94</v>
+        <v>1528.36</v>
       </c>
       <c r="I2">
-        <v>18046</v>
+        <v>18076</v>
       </c>
       <c r="J2">
-        <v>7.18</v>
+        <v>9.76</v>
       </c>
       <c r="K2">
-        <v>912.85</v>
+        <v>1177.95</v>
       </c>
       <c r="L2">
-        <v>940.99</v>
+        <v>1216.21</v>
       </c>
     </row>
     <row r="3">
@@ -608,37 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>511.98</v>
+        <v>668.35</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>11402.79</v>
+        <v>24790.59</v>
       </c>
       <c r="E3">
-        <v>809.48</v>
+        <v>1096.66</v>
       </c>
       <c r="F3">
-        <v>210.29</v>
+        <v>267.38</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>672.92</v>
+        <v>894.3</v>
       </c>
       <c r="I3">
-        <v>18046</v>
+        <v>18076</v>
       </c>
       <c r="J3">
-        <v>6.03</v>
+        <v>8.16</v>
       </c>
       <c r="K3">
-        <v>500.17</v>
+        <v>652.36</v>
       </c>
       <c r="L3">
-        <v>523.79</v>
+        <v>684.34</v>
       </c>
     </row>
   </sheetData>
